--- a/reports/月度检查包_2026年06月_华东区/月度检查包_2026年06月_华东区.xlsx
+++ b/reports/月度检查包_2026年06月_华东区/月度检查包_2026年06月_华东区.xlsx
@@ -477,7 +477,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-09 01:23:55</t>
+          <t>2026-06-09 01:40:20</t>
         </is>
       </c>
     </row>
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -522,7 +522,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11">
@@ -552,7 +552,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -566,7 +566,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -590,7 +590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M19"/>
+  <dimension ref="A1:M15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -673,7 +673,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>涉及13项/已检查4项/隐患1项</t>
+          <t>涉及13项/已检查1项/隐患1项</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
@@ -687,7 +687,7 @@
       <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
-          <t>PLBD8C195CADB9</t>
+          <t>PL45FFDB0672FD</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -712,7 +712,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>已完成</t>
+          <t>有隐患</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -729,7 +729,7 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>压力正常/标签完好；正常检查</t>
+          <t>压力正常/标签完好；正常检查；手工追加：后来发现密封垫老化</t>
         </is>
       </c>
       <c r="M3" t="n">
@@ -740,7 +740,7 @@
       <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PL486C95CA38C4</t>
+          <t>PLF627D373409A</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>已完成</t>
+          <t>待执行</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -773,31 +773,19 @@
           <t>2026-06-09</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>压力正常；延期1天检查</t>
-        </is>
-      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PL80CD126A08D8</t>
+          <t>PLF3D7FC8E4C2F</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -822,7 +810,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>有隐患</t>
+          <t>待执行</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -830,31 +818,19 @@
           <t>2026-06-09</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>压力不足；延期2天发现隐患</t>
-        </is>
-      </c>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PLF3C1DE7AFC78</t>
+          <t>PL6AAB0FDBE6AB</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -899,7 +875,7 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>PL40CF83537F2E</t>
+          <t>PL81C3087415A3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -944,7 +920,7 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>PL5A398200ED19</t>
+          <t>PL8AF83FC473BC</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -969,7 +945,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>已完成</t>
+          <t>待执行</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -977,18 +953,10 @@
           <t>2026-06-09</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>未填状态会推断；空状态推断</t>
-        </is>
-      </c>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
         <v>0</v>
       </c>
@@ -997,7 +965,7 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>PL5FC9D55F3FCB</t>
+          <t>PLAC7909B7B1C6</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1042,7 +1010,7 @@
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
-          <t>PL433BA1F725BB</t>
+          <t>PLF8A0C2D39AB5</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1087,7 +1055,7 @@
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>PLD83A31853DFD</t>
+          <t>PL9576881AF2D9</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1132,7 +1100,7 @@
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
-          <t>PL431AB549ED6B</t>
+          <t>PL4934A4247F74</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1177,7 +1145,7 @@
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
-          <t>PL91E85822147D</t>
+          <t>PLFD8FDBDF6F80</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1222,7 +1190,7 @@
       <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
-          <t>PLD253F7CF8E53</t>
+          <t>PL56DA8F90B2CD</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1267,7 +1235,7 @@
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
-          <t>PL6779B5403F5B</t>
+          <t>PL241CC86D1EAE</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1306,166 +1274,6 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="n">
         <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>--- 2026-06-10 ---</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>涉及1项/已检查1项/隐患0项</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr"/>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>PL486C95CA38C4</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>FH-002</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>灭火器MFZ/ABC4</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>1号楼</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>1层</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>已完成</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>压力正常；延期1天检查</t>
-        </is>
-      </c>
-      <c r="M17" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>--- 2026-06-11 ---</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>涉及1项/已检查1项/隐患1项</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>PL80CD126A08D8</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>FH-003</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>灭火器MFZ/ABC4</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>1号楼</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2层</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>有隐患</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>压力不足；延期2天发现隐患</t>
-        </is>
-      </c>
-      <c r="M19" t="n">
-        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -1479,152 +1287,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>隐患编号</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>设备编号</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>严重程度</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>状态</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>是否逾期</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>楼栋</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>楼层</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>区域</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>发现日期</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>整改期限</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>登记人</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>隐患描述</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>整改措施</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>复查人</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>关闭日期</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>IS483F91457718</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>FH-001</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>一般</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>待整改</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>1号楼</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>1层</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>华东区</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>system</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>故意模拟老数据，不传楼层</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1635,214 +1300,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>来源类型</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>编号</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>关联设备</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>设备名称</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>楼栋/楼层</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>计划日期</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>实际检查日期</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>当前状态</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>缺失字段</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>备注</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>计划</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>PL5A398200ED19</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>FH-006</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>灭火器MFZ/ABC4</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>1号楼 3层</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>已完成</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>photo_paths</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>未填状态会推断；空状态推断</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>计划</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>PL5A398200ED19</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>FH-006</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>灭火器MFZ/ABC4</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>1号楼 3层</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>已完成</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>photo_paths</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>未填状态会推断；空状态推断</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>隐患(整改前)</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>IS483F91457718</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>FH-001</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>灭火器MFZ/ABC4</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>1号楼 1层</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>待整改</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>photo_before</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>故意模拟老数据，不传楼层</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1853,7 +1313,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:L3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1912,6 +1372,11 @@
           <t>文件大小(字节)</t>
         </is>
       </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>包内路径</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1921,7 +1386,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>PLBD8C195CADB9</t>
+          <t>PL45FFDB0672FD</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1947,7 +1412,7 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>已完成</t>
+          <t>有隐患</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -1957,12 +1422,17 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>attachments\PLBD8C195CADB9\20260609_012329_FH001_灭火器.jpg</t>
+          <t>attachments\PL45FFDB0672FD\20260609_013834_FH001_灭火器.jpg</t>
         </is>
       </c>
       <c r="K2" t="n">
         <v>30</v>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>附件照片/20260609_013834_FH001_灭火器_1.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1972,12 +1442,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>PL486C95CA38C4</t>
+          <t>PL45FFDB0672FD</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>FH-002</t>
+          <t>FH-001</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1992,17 +1462,13 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>已完成</t>
+          <t>有隐患</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -2012,337 +1478,16 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>attachments\PL486C95CA38C4\20260609_012329_FH002_应急灯.jpg</t>
+          <t>attachments\PL45FFDB0672FD\20260609_013834_FH001_灭火器.jpg</t>
         </is>
       </c>
       <c r="K3" t="n">
         <v>30</v>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>巡检计划</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>PL80CD126A08D8</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>FH-003</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>灭火器MFZ/ABC4</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>有隐患</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1/2</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>attachments\PL80CD126A08D8\20260609_012329_FH003_消火栓.jpg</t>
-        </is>
-      </c>
-      <c r="K4" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>巡检计划</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>PL80CD126A08D8</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>FH-003</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>灭火器MFZ/ABC4</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>有隐患</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2/2</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>attachments\PL80CD126A08D8\20260609_012329_隐患照片1.jpg</t>
-        </is>
-      </c>
-      <c r="K5" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>巡检计划</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>PLBD8C195CADB9</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>FH-001</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>灭火器MFZ/ABC4</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>已完成</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1/1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>attachments\PLBD8C195CADB9\20260609_012329_FH001_灭火器.jpg</t>
-        </is>
-      </c>
-      <c r="K6" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>巡检计划</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>PL486C95CA38C4</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>FH-002</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>灭火器MFZ/ABC4</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>已完成</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1/1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>attachments\PL486C95CA38C4\20260609_012329_FH002_应急灯.jpg</t>
-        </is>
-      </c>
-      <c r="K7" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>巡检计划</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>PL80CD126A08D8</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>FH-003</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>灭火器MFZ/ABC4</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>有隐患</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1/2</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>attachments\PL80CD126A08D8\20260609_012329_FH003_消火栓.jpg</t>
-        </is>
-      </c>
-      <c r="K8" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>巡检计划</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>PL80CD126A08D8</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>FH-003</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>灭火器MFZ/ABC4</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>有隐患</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2/2</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>attachments\PL80CD126A08D8\20260609_012329_隐患照片1.jpg</t>
-        </is>
-      </c>
-      <c r="K9" t="n">
-        <v>30</v>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>附件照片/20260609_013834_FH001_灭火器_1.jpg</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -2356,169 +1501,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>计划编号</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>设备编号</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>设备名称</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>楼栋</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>楼层</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>计划日期</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>实际检查日期</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>延期天数</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>巡检人</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>状态</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>检查结果</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>PL486C95CA38C4</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>FH-002</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>灭火器MFZ/ABC4</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>1号楼</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>1层</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>已完成</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>压力正常；延期1天检查</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>PL80CD126A08D8</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>FH-003</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>灭火器MFZ/ABC4</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>1号楼</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2层</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>2</v>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>有隐患</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>压力不足；延期2天发现隐患</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>